--- a/Result/profitability/2892.xlsx
+++ b/Result/profitability/2892.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM93"/>
+  <dimension ref="A1:AM94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
         <v>0.42</v>
       </c>
       <c r="M2" t="n">
-        <v>0.45</v>
+        <v>0.46125</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
@@ -766,7 +766,7 @@
         <v>0.47</v>
       </c>
       <c r="M3" t="n">
-        <v>0.44875</v>
+        <v>0.4575</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
@@ -877,7 +877,7 @@
         <v>-3.92</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.10375</v>
+        <v>-0.07250000000000001</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -988,7 +988,7 @@
         <v>0.38</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.09624999999999999</v>
+        <v>-0.08875000000000001</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
@@ -1099,7 +1099,7 @@
         <v>0.62</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.08249999999999998</v>
+        <v>-0.07000000000000002</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1218,7 +1218,7 @@
         <v>0.48</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.08124999999999999</v>
+        <v>-0.07750000000000001</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -1331,7 +1331,7 @@
         <v>0.4</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.09874999999999999</v>
+        <v>-0.07250000000000001</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -10653,6 +10653,113 @@
         <v>114.4</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>115.1Q</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>19297</v>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="n">
+        <v>10036</v>
+      </c>
+      <c r="K94" t="n">
+        <v>8244</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="n">
+        <v>1</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>1</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" t="n">
+        <v>1</v>
+      </c>
+      <c r="V94" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="W94" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="X94" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="Y94" t="inlineStr"/>
+      <c r="Z94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>0.05999999999999994</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>0.1176470588235292</v>
+      </c>
+      <c r="AC94" t="inlineStr"/>
+      <c r="AD94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK94" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM94" t="n">
+        <v>115.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
